--- a/data/trans_orig/P58-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P58-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2007</t>
+          <t>Población según su lugar de nacimiento en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23759</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51422</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22835</t>
+          <t>22934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>32263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64659</t>
+          <t>65079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39975</t>
+          <t>41145</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75355</t>
+          <t>75598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21869</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46530</t>
+          <t>45586</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71660</t>
+          <t>70372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113520</t>
+          <t>110315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>360858</t>
+          <t>359533</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>401949</t>
+          <t>400846</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>243346</t>
+          <t>248371</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274151</t>
+          <t>274570</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>617600</t>
+          <t>619417</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>667712</t>
+          <t>666205</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35052</t>
+          <t>36544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>37711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>31806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65465</t>
+          <t>64422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40110</t>
+          <t>40561</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74586</t>
+          <t>74972</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32486</t>
+          <t>33705</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60282</t>
+          <t>59388</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>80679</t>
+          <t>82394</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>123083</t>
+          <t>124668</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>267505</t>
+          <t>267730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>304635</t>
+          <t>306954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>284357</t>
+          <t>284999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>318306</t>
+          <t>318321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,47 +1465,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>76,64%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>85,6%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>590398</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>564988</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>613526</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>79,91%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>76,47%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>85,6%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>590398</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>566036</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>615956</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>79,91%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40394</t>
+          <t>41056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51088</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37789</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72476</t>
+          <t>71508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>11328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28517</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>53214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92321</t>
+          <t>92784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>442955</t>
+          <t>438664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>482945</t>
+          <t>479944</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129496</t>
+          <t>131938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151629</t>
+          <t>151669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>579004</t>
+          <t>580291</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>625443</t>
+          <t>625490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,08%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47385</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84625</t>
+          <t>89105</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50162</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86434</t>
+          <t>89034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108487</t>
+          <t>107080</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164565</t>
+          <t>160437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55141</t>
+          <t>53694</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99179</t>
+          <t>95821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>33156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61317</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96086</t>
+          <t>97901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146683</t>
+          <t>147882</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1070384</t>
+          <t>1071216</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1124788</t>
+          <t>1128723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>579355</t>
+          <t>578700</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>622013</t>
+          <t>622929</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1661128</t>
+          <t>1661937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1732890</t>
+          <t>1732202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54821</t>
+          <t>54831</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50140</t>
+          <t>50394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88042</t>
+          <t>88943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84639</t>
+          <t>84382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132876</t>
+          <t>134743</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34228</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>45171</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69771</t>
+          <t>69100</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>274193</t>
+          <t>272544</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>308077</t>
+          <t>307780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>445626</t>
+          <t>446559</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>488879</t>
+          <t>488801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>730738</t>
+          <t>730695</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>786154</t>
+          <t>786782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26841</t>
+          <t>25783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31855</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64292</t>
+          <t>64970</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44903</t>
+          <t>46655</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83259</t>
+          <t>83824</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23841</t>
+          <t>24191</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57746</t>
+          <t>57837</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90853</t>
+          <t>92894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70072</t>
+          <t>69095</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107590</t>
+          <t>108265</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>257142</t>
+          <t>256138</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>281243</t>
+          <t>280884</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1103036</t>
+          <t>1104303</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1149684</t>
+          <t>1148977</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1370745</t>
+          <t>1373085</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1422276</t>
+          <t>1423590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>169382</t>
+          <t>169440</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>242667</t>
+          <t>240276</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>193611</t>
+          <t>191312</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>263388</t>
+          <t>262291</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>382641</t>
+          <t>380191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>477287</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>236174</t>
+          <t>235269</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>318159</t>
+          <t>313384</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>219627</t>
+          <t>219486</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>282471</t>
+          <t>284807</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>469671</t>
+          <t>469267</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>575302</t>
+          <t>573420</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2739668</t>
+          <t>2745760</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2839847</t>
+          <t>2844338</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2853638</t>
+          <t>2856239</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2947639</t>
+          <t>2948556</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5629070</t>
+          <t>5631629</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5759427</t>
+          <t>5758186</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2012</t>
+          <t>Población según su lugar de nacimiento en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34191</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52622</t>
+          <t>51605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47994</t>
+          <t>45519</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86906</t>
+          <t>86617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43092</t>
+          <t>43733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80430</t>
+          <t>78348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100756</t>
+          <t>101943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155014</t>
+          <t>158735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>336340</t>
+          <t>335120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>376255</t>
+          <t>377900</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>210966</t>
+          <t>213040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>250048</t>
+          <t>250071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>558541</t>
+          <t>559050</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>615668</t>
+          <t>615987</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>26157</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>23269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49322</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58478</t>
+          <t>60805</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103286</t>
+          <t>105375</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47035</t>
+          <t>47255</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84088</t>
+          <t>82885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>120789</t>
+          <t>118130</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179261</t>
+          <t>179549</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>296686</t>
+          <t>296519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>340189</t>
+          <t>341447</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>238096</t>
+          <t>236723</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>276522</t>
+          <t>274497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>542600</t>
+          <t>541935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>602356</t>
+          <t>603843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47050</t>
+          <t>46336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>32465</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61237</t>
+          <t>60448</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48592</t>
+          <t>48465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91427</t>
+          <t>92084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>32056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65069</t>
+          <t>64151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115222</t>
+          <t>113192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>503367</t>
+          <t>500521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>549871</t>
+          <t>549621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>213438</t>
+          <t>214002</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>238940</t>
+          <t>239990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>729741</t>
+          <t>731447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783315</t>
+          <t>783380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65551</t>
+          <t>65843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104149</t>
+          <t>105623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51947</t>
+          <t>52779</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85675</t>
+          <t>85653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126739</t>
+          <t>120953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178440</t>
+          <t>174248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87903</t>
+          <t>90500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143783</t>
+          <t>145419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60964</t>
+          <t>61745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106379</t>
+          <t>106098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165025</t>
+          <t>165184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232011</t>
+          <t>236028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>931050</t>
+          <t>928619</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>993151</t>
+          <t>991073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>589088</t>
+          <t>590196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>643802</t>
+          <t>642337</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1538513</t>
+          <t>1538018</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1619971</t>
+          <t>1619125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>34550</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63244</t>
+          <t>65310</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46086</t>
+          <t>45486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>79174</t>
+          <t>77044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>87502</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129725</t>
+          <t>131056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>29466</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39213</t>
+          <t>40499</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78002</t>
+          <t>78608</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>52268</t>
+          <t>51007</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>95472</t>
+          <t>94419</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>429986</t>
+          <t>426511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>463384</t>
+          <t>463761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>619036</t>
+          <t>619116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>664873</t>
+          <t>668435</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1062703</t>
+          <t>1061885</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1118957</t>
+          <t>1120360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36986</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66684</t>
+          <t>66538</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,47 +6489,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>64223</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>48921</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>82770</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>6,01%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>64223</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>49613</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>83635</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>24329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50337</t>
+          <t>49755</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94876</t>
+          <t>90508</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60893</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106271</t>
+          <t>104950</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>227026</t>
+          <t>225746</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>250820</t>
+          <t>251099</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>961733</t>
+          <t>964413</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1011691</t>
+          <t>1012365</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1201079</t>
+          <t>1204565</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1255549</t>
+          <t>1257568</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181275</t>
+          <t>178965</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>241094</t>
+          <t>241546</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>200942</t>
+          <t>201155</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>263195</t>
+          <t>261080</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>395462</t>
+          <t>398509</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>483593</t>
+          <t>487184</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>312915</t>
+          <t>310462</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>407235</t>
+          <t>406865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>305334</t>
+          <t>312744</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>400304</t>
+          <t>401093</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>645773</t>
+          <t>640978</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>780585</t>
+          <t>769603</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2798401</t>
+          <t>2798196</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2910654</t>
+          <t>2909727</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2915982</t>
+          <t>2913100</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3021908</t>
+          <t>3016653</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5745462</t>
+          <t>5748113</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5898400</t>
+          <t>5900139</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2016</t>
+          <t>Población según su lugar de nacimiento en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>26870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53029</t>
+          <t>52521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>36180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>79423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45308</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84053</t>
+          <t>80584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24675</t>
+          <t>26341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55228</t>
+          <t>57021</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77328</t>
+          <t>76784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124001</t>
+          <t>124877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>306250</t>
+          <t>309086</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>348356</t>
+          <t>351038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>266938</t>
+          <t>265848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>300966</t>
+          <t>300183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>583367</t>
+          <t>589708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>638672</t>
+          <t>641721</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>43659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26234</t>
+          <t>25632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51652</t>
+          <t>50611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>45480</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78793</t>
+          <t>79481</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>34561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68392</t>
+          <t>68136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>88860</t>
+          <t>89430</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>137287</t>
+          <t>138802</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>291500</t>
+          <t>291271</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>327388</t>
+          <t>326724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>272314</t>
+          <t>271481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>308179</t>
+          <t>308139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>570522</t>
+          <t>572735</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>624085</t>
+          <t>625208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36074</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36966</t>
+          <t>37175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70733</t>
+          <t>68343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38015</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55857</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95182</t>
+          <t>97102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>426363</t>
+          <t>430097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>464502</t>
+          <t>465626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119894</t>
+          <t>120863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145061</t>
+          <t>145724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>560215</t>
+          <t>559459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>602281</t>
+          <t>603377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>66401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54003</t>
+          <t>52315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86270</t>
+          <t>85302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97660</t>
+          <t>97372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143174</t>
+          <t>142930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62243</t>
+          <t>61478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106518</t>
+          <t>105714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61285</t>
+          <t>61013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104305</t>
+          <t>103386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132963</t>
+          <t>133486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>193998</t>
+          <t>195534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>989998</t>
+          <t>990245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1040237</t>
+          <t>1039973</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>652838</t>
+          <t>652051</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>699755</t>
+          <t>700559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1656708</t>
+          <t>1657053</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1729742</t>
+          <t>1728328</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,49%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45373</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78396</t>
+          <t>76504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43095</t>
+          <t>43673</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71661</t>
+          <t>72293</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>95953</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140228</t>
+          <t>139144</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29967</t>
+          <t>29951</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63646</t>
+          <t>63203</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39528</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72454</t>
+          <t>74159</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76811</t>
+          <t>80208</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>125399</t>
+          <t>128300</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>492641</t>
+          <t>493398</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>537190</t>
+          <t>536716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>604096</t>
+          <t>604302</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>645703</t>
+          <t>647348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1109364</t>
+          <t>1108446</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1174636</t>
+          <t>1171220</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>42999</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>29763</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55685</t>
+          <t>55816</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53799</t>
+          <t>55741</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87560</t>
+          <t>89091</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57502</t>
+          <t>56862</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102798</t>
+          <t>99732</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69019</t>
+          <t>69629</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117730</t>
+          <t>118226</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>227216</t>
+          <t>225670</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>256180</t>
+          <t>255477</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>935530</t>
+          <t>938611</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>985204</t>
+          <t>987520</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1176743</t>
+          <t>1176667</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1233430</t>
+          <t>1235144</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>176732</t>
+          <t>179784</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>235929</t>
+          <t>238570</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>198488</t>
+          <t>202901</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>259394</t>
+          <t>259115</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>394475</t>
+          <t>393846</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>485262</t>
+          <t>478109</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>274514</t>
+          <t>274941</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>358589</t>
+          <t>360726</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>286437</t>
+          <t>285904</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>370593</t>
+          <t>371450</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>582407</t>
+          <t>584841</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>707402</t>
+          <t>707680</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2813161</t>
+          <t>2811067</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2914210</t>
+          <t>2915317</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2920546</t>
+          <t>2924256</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3025204</t>
+          <t>3019522</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5765405</t>
+          <t>5767303</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5914930</t>
+          <t>5905251</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2023</t>
+          <t>Población según su lugar de nacimiento en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>37765</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66786</t>
+          <t>64022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31822</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51975</t>
+          <t>51283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75399</t>
+          <t>74530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109523</t>
+          <t>107639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>433666</t>
+          <t>435811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>460848</t>
+          <t>462700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>387717</t>
+          <t>388349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>408147</t>
+          <t>408528</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>829285</t>
+          <t>831145</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>864557</t>
+          <t>864914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10376</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>13751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>32448</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58928</t>
+          <t>59319</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>34793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>54406</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>85951</t>
+          <t>86396</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>389855</t>
+          <t>389688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>417393</t>
+          <t>416737</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>338434</t>
+          <t>339555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>355052</t>
+          <t>355332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>736823</t>
+          <t>736416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>768452</t>
+          <t>769077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>29032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>17599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41168</t>
+          <t>41727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>390087</t>
+          <t>389384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>408437</t>
+          <t>407666</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146693</t>
+          <t>147079</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157919</t>
+          <t>157994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541065</t>
+          <t>541487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>563043</t>
+          <t>562593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25704</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34719</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46448</t>
+          <t>46290</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35492</t>
+          <t>35094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57545</t>
+          <t>55931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63028</t>
+          <t>62482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95838</t>
+          <t>95973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>967419</t>
+          <t>967753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>991864</t>
+          <t>992213</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>696808</t>
+          <t>697863</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>719618</t>
+          <t>719479</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1672358</t>
+          <t>1672465</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1705591</t>
+          <t>1706952</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34565</t>
+          <t>35367</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,47 +12963,47 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>23263</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>16123</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>31749</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>2,21%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>23263</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>16205</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>31898</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>31535</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58992</t>
+          <t>58162</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>428433</t>
+          <t>427374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>452409</t>
+          <t>452363</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>683699</t>
+          <t>682753</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>700073</t>
+          <t>700042</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1119092</t>
+          <t>1118885</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1148039</t>
+          <t>1146927</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>28901</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>35009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,47 +13454,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>31191</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>20591</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>51810</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>31191</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>20850</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>48562</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>215759</t>
+          <t>209823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>238367</t>
+          <t>238251</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>714097</t>
+          <t>714933</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>733635</t>
+          <t>733393</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>939234</t>
+          <t>936213</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>967415</t>
+          <t>968105</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>34534</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44974</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51621</t>
+          <t>52281</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63494</t>
+          <t>64465</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89139</t>
+          <t>89010</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>105593</t>
+          <t>104580</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>145866</t>
+          <t>144891</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>202690</t>
+          <t>199592</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>146555</t>
+          <t>149128</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>190879</t>
+          <t>193699</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,47 +13910,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>339457</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>303797</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>374010</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>5,87%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>339457</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>308300</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>378431</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2880939</t>
+          <t>2883584</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2938093</t>
+          <t>2939945</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3005611</t>
+          <t>3001554</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3050651</t>
+          <t>3048473</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5900372</t>
+          <t>5905287</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5973683</t>
+          <t>5977000</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P58-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P58-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>24553</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51201</t>
+          <t>52165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>22415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32263</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65079</t>
+          <t>68318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41145</t>
+          <t>40579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75598</t>
+          <t>75398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>23743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45586</t>
+          <t>48774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70372</t>
+          <t>71752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110315</t>
+          <t>113426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>359533</t>
+          <t>358900</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>400846</t>
+          <t>401253</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>248371</t>
+          <t>243516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274570</t>
+          <t>273159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>619417</t>
+          <t>618192</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>666205</t>
+          <t>667273</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36544</t>
+          <t>36097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,47 +1204,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>24307</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13396</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38760</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>24307</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14740</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37711</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31806</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64422</t>
+          <t>64965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40561</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74972</t>
+          <t>75751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>32747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>60410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>82394</t>
+          <t>80770</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>124668</t>
+          <t>123591</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>267730</t>
+          <t>269010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>306954</t>
+          <t>305811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>284999</t>
+          <t>285744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>318321</t>
+          <t>318466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>564988</t>
+          <t>564439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>613526</t>
+          <t>614605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41056</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>21047</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49834</t>
+          <t>51880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37083</t>
+          <t>36232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71508</t>
+          <t>71769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11328</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>27775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53214</t>
+          <t>54818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92784</t>
+          <t>91261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>438664</t>
+          <t>442560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>479944</t>
+          <t>482499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>131938</t>
+          <t>131502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151669</t>
+          <t>151556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>580291</t>
+          <t>578998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>625490</t>
+          <t>625314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48651</t>
+          <t>46705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89105</t>
+          <t>84538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50098</t>
+          <t>49729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89034</t>
+          <t>86131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107080</t>
+          <t>107533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160437</t>
+          <t>162790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53694</t>
+          <t>55165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95821</t>
+          <t>98450</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33156</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62564</t>
+          <t>61741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97901</t>
+          <t>93960</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>147882</t>
+          <t>146654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1071216</t>
+          <t>1067641</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1128723</t>
+          <t>1124331</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>578700</t>
+          <t>578714</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>622929</t>
+          <t>622338</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1661937</t>
+          <t>1664398</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1732202</t>
+          <t>1736217</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54831</t>
+          <t>54785</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50394</t>
+          <t>51267</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88943</t>
+          <t>88913</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84382</t>
+          <t>84569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134743</t>
+          <t>131861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>33766</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>21672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45171</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>37765</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69100</t>
+          <t>69950</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>272544</t>
+          <t>273463</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>307780</t>
+          <t>308311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>446559</t>
+          <t>444327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>488801</t>
+          <t>487401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>730695</t>
+          <t>730668</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>786782</t>
+          <t>786493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>27438</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31900</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64970</t>
+          <t>63889</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46655</t>
+          <t>46537</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83824</t>
+          <t>82845</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24191</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57837</t>
+          <t>58422</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92894</t>
+          <t>95342</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69095</t>
+          <t>68994</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>108265</t>
+          <t>107315</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>256138</t>
+          <t>256672</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>280884</t>
+          <t>281234</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1104303</t>
+          <t>1100889</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1148977</t>
+          <t>1149223</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1373085</t>
+          <t>1369153</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1423590</t>
+          <t>1421500</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>169440</t>
+          <t>171895</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>240276</t>
+          <t>241455</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>191312</t>
+          <t>195191</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>262291</t>
+          <t>263899</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>380191</t>
+          <t>382019</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>477287</t>
+          <t>482976</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>235269</t>
+          <t>235930</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>313384</t>
+          <t>315603</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>219486</t>
+          <t>221455</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>284807</t>
+          <t>281981</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>469267</t>
+          <t>474769</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>573420</t>
+          <t>576266</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2745760</t>
+          <t>2741793</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2844338</t>
+          <t>2841093</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2856239</t>
+          <t>2858313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2948556</t>
+          <t>2947513</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5631629</t>
+          <t>5628787</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5758186</t>
+          <t>5761933</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34828</t>
+          <t>34277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51605</t>
+          <t>51621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45519</t>
+          <t>45782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86617</t>
+          <t>87345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43733</t>
+          <t>44176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78348</t>
+          <t>79399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101943</t>
+          <t>97631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158735</t>
+          <t>152518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>335120</t>
+          <t>332901</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>377900</t>
+          <t>377596</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>213040</t>
+          <t>213016</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>250071</t>
+          <t>251074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>559050</t>
+          <t>562192</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>615987</t>
+          <t>619773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29459</t>
+          <t>28625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26157</t>
+          <t>27259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23269</t>
+          <t>23063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49947</t>
+          <t>48356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>62772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105375</t>
+          <t>107465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47255</t>
+          <t>45391</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82885</t>
+          <t>82932</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118130</t>
+          <t>119950</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179549</t>
+          <t>176897</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>296519</t>
+          <t>294286</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>341447</t>
+          <t>339735</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>236723</t>
+          <t>236788</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274497</t>
+          <t>275936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>541935</t>
+          <t>544487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>603843</t>
+          <t>604557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46336</t>
+          <t>45850</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32465</t>
+          <t>33445</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60448</t>
+          <t>63081</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48465</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92084</t>
+          <t>93867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32056</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64151</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113192</t>
+          <t>112982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500521</t>
+          <t>502275</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>549621</t>
+          <t>550082</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214002</t>
+          <t>213354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>239990</t>
+          <t>238921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>731447</t>
+          <t>727193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783380</t>
+          <t>781257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65843</t>
+          <t>64808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105623</t>
+          <t>102772</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52779</t>
+          <t>50913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85653</t>
+          <t>84445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120953</t>
+          <t>125755</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174248</t>
+          <t>175101</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90500</t>
+          <t>88526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145419</t>
+          <t>142691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61745</t>
+          <t>63158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106098</t>
+          <t>107089</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165184</t>
+          <t>162778</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236028</t>
+          <t>232811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>928619</t>
+          <t>930763</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>991073</t>
+          <t>991682</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>590196</t>
+          <t>588254</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>642337</t>
+          <t>640663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1538018</t>
+          <t>1536967</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1619125</t>
+          <t>1615411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34550</t>
+          <t>33910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65310</t>
+          <t>63227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45486</t>
+          <t>45128</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77044</t>
+          <t>77513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87502</t>
+          <t>88364</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>131056</t>
+          <t>131946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29466</t>
+          <t>31470</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40499</t>
+          <t>39091</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78608</t>
+          <t>78279</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>51280</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>94419</t>
+          <t>95541</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>426511</t>
+          <t>428739</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>463761</t>
+          <t>464698</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>619116</t>
+          <t>619079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>668435</t>
+          <t>667863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1061885</t>
+          <t>1059517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1120360</t>
+          <t>1118213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>24193</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36688</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66538</t>
+          <t>65695</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>48921</t>
+          <t>49305</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>82770</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24329</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>50066</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>93241</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58500</t>
+          <t>60410</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104950</t>
+          <t>106031</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>225746</t>
+          <t>228443</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>251099</t>
+          <t>251844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>964413</t>
+          <t>962744</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1012365</t>
+          <t>1012672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1204565</t>
+          <t>1201341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1257568</t>
+          <t>1255783</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178965</t>
+          <t>181027</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>241546</t>
+          <t>242663</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>201155</t>
+          <t>201076</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>261080</t>
+          <t>263113</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>398509</t>
+          <t>397045</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>487184</t>
+          <t>484347</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>310462</t>
+          <t>308964</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>406865</t>
+          <t>405381</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>312744</t>
+          <t>309787</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>401093</t>
+          <t>400548</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>640978</t>
+          <t>640495</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>769603</t>
+          <t>783924</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2798196</t>
+          <t>2803478</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2909727</t>
+          <t>2908549</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2913100</t>
+          <t>2915047</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3016653</t>
+          <t>3017842</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5748113</t>
+          <t>5742261</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5900139</t>
+          <t>5903184</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>27523</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52521</t>
+          <t>51940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36180</t>
+          <t>35667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47448</t>
+          <t>46417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79423</t>
+          <t>79637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>43387</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80584</t>
+          <t>80142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>55200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76784</t>
+          <t>78473</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124877</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>309086</t>
+          <t>309227</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>351038</t>
+          <t>349897</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>265848</t>
+          <t>266488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>300183</t>
+          <t>297653</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>589708</t>
+          <t>586400</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>641721</t>
+          <t>639412</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>14618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>21128</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43659</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>26300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50611</t>
+          <t>51809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45480</t>
+          <t>43432</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79481</t>
+          <t>77974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34561</t>
+          <t>35958</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68136</t>
+          <t>67971</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89430</t>
+          <t>89580</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>138802</t>
+          <t>138004</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>291271</t>
+          <t>291982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>326724</t>
+          <t>327150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>271481</t>
+          <t>272318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>308139</t>
+          <t>307873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>572735</t>
+          <t>573249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>625208</t>
+          <t>624662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>34520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>20897</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46360</t>
+          <t>45178</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37175</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68343</t>
+          <t>71212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>13421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36700</t>
+          <t>36174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55890</t>
+          <t>56573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97102</t>
+          <t>94834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>430097</t>
+          <t>427181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>465626</t>
+          <t>464785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120863</t>
+          <t>121407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145724</t>
+          <t>145252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>559459</t>
+          <t>558320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>603377</t>
+          <t>601317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>68841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52315</t>
+          <t>52468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85302</t>
+          <t>87616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97372</t>
+          <t>99518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142930</t>
+          <t>143064</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>63347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105714</t>
+          <t>104886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>60074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>103399</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133486</t>
+          <t>133578</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195534</t>
+          <t>195395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>990245</t>
+          <t>990240</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1039973</t>
+          <t>1039886</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>652051</t>
+          <t>651137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>700559</t>
+          <t>701182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1657053</t>
+          <t>1657125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1728328</t>
+          <t>1727344</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43718</t>
+          <t>44823</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76504</t>
+          <t>77432</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43673</t>
+          <t>42576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72293</t>
+          <t>70839</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95953</t>
+          <t>94282</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>139144</t>
+          <t>137222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29951</t>
+          <t>28519</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63203</t>
+          <t>61540</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74159</t>
+          <t>78543</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>80208</t>
+          <t>76558</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128300</t>
+          <t>125029</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>493398</t>
+          <t>494105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>536716</t>
+          <t>537225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,82 +9650,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>86,55%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>626468</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>603947</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>646103</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>84,86%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>81,81%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1137</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1143606</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1113270</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1175113</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>84,15%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>81,92%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>86,47%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>626468</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>604302</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>647348</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>81,86%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>87,69%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1137</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1143606</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1108446</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1171220</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>84,15%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>81,57%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>42624</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55816</t>
+          <t>54663</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>55741</t>
+          <t>55215</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89091</t>
+          <t>88668</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27609</t>
+          <t>28209</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56862</t>
+          <t>56231</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>99732</t>
+          <t>99913</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69629</t>
+          <t>72906</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>118226</t>
+          <t>120642</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>225670</t>
+          <t>225107</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>255477</t>
+          <t>255633</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>938611</t>
+          <t>939413</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>987520</t>
+          <t>988982</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1176667</t>
+          <t>1175373</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1235144</t>
+          <t>1232190</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>179784</t>
+          <t>177496</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238570</t>
+          <t>241321</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>202901</t>
+          <t>200256</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>259115</t>
+          <t>262753</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>393846</t>
+          <t>397195</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>478109</t>
+          <t>483071</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>274941</t>
+          <t>275783</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>360726</t>
+          <t>358623</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>285904</t>
+          <t>283752</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>371450</t>
+          <t>370271</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>584841</t>
+          <t>576800</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>707680</t>
+          <t>699640</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2811067</t>
+          <t>2809086</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2915317</t>
+          <t>2911661</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2924256</t>
+          <t>2927681</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3019522</t>
+          <t>3028716</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5767303</t>
+          <t>5770968</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5905251</t>
+          <t>5908553</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>37111</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>25735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>50157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>31791</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>43669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>68902</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>85794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50122</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>38696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64022</t>
+          <t>65735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>40639</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>31065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51283</t>
+          <t>51954</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>90116</t>
+          <t>91916</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74530</t>
+          <t>76342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107639</t>
+          <t>109602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>449691</t>
+          <t>462230</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>435811</t>
+          <t>443460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>462700</t>
+          <t>478117</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>399327</t>
+          <t>414913</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>388349</t>
+          <t>400618</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>408528</t>
+          <t>427768</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>849018</t>
+          <t>877142</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>831145</t>
+          <t>855663</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>864914</t>
+          <t>900190</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>446426</t>
+          <t>487342</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446426</t>
+          <t>487342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>446426</t>
+          <t>487342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>951638</t>
+          <t>1037960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951638</t>
+          <t>1037960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>951638</t>
+          <t>1037960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>33954</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>44941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>52377</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>41013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>68178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32448</t>
+          <t>32774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59319</t>
+          <t>60945</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>27243</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19163</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34793</t>
+          <t>36692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69413</t>
+          <t>72091</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>54406</t>
+          <t>58039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>86396</t>
+          <t>90928</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>405995</t>
+          <t>419941</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>389688</t>
+          <t>401272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>416737</t>
+          <t>433905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>347856</t>
+          <t>361237</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>339555</t>
+          <t>347326</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>355332</t>
+          <t>373102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>753851</t>
+          <t>781178</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>736416</t>
+          <t>759138</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>769077</t>
+          <t>799032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>381915</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381915</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381915</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834128</t>
+          <t>905646</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834128</t>
+          <t>905646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834128</t>
+          <t>905646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>52837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>49171</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>66083</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29032</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>29137</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>42452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>400289</t>
+          <t>415296</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>389384</t>
+          <t>397793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407666</t>
+          <t>429406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>153565</t>
+          <t>163558</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147079</t>
+          <t>154137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157994</t>
+          <t>170274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>553854</t>
+          <t>578854</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541487</t>
+          <t>559475</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>562593</t>
+          <t>594922</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423584</t>
+          <t>470471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>423584</t>
+          <t>470471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423584</t>
+          <t>470471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>590495</t>
+          <t>657968</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>590495</t>
+          <t>657968</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>590495</t>
+          <t>657968</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>92346</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>72418</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>114839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>68031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>98947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>174356</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>148441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>203662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32821</t>
+          <t>33924</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46290</t>
+          <t>47364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44913</t>
+          <t>46039</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35094</t>
+          <t>35522</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55931</t>
+          <t>59803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>77734</t>
+          <t>79963</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62482</t>
+          <t>64392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95973</t>
+          <t>96402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>980749</t>
+          <t>1004391</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>967753</t>
+          <t>979238</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>992213</t>
+          <t>1025807</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>709694</t>
+          <t>731643</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>697863</t>
+          <t>710726</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>719479</t>
+          <t>748097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1690442</t>
+          <t>1736034</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1672465</t>
+          <t>1701405</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1706952</t>
+          <t>1763918</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1025858</t>
+          <t>1130661</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1025858</t>
+          <t>1130661</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1025858</t>
+          <t>1130661</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>772163</t>
+          <t>859693</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>772163</t>
+          <t>859693</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>772163</t>
+          <t>859693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1798020</t>
+          <t>1990354</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1798020</t>
+          <t>1990354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1798020</t>
+          <t>1990354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>93467</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>74546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>116589</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>75852</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>61591</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>92504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>27844</t>
+          <t>169319</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>144311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32461</t>
+          <t>197007</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23263</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31749</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>41236</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31535</t>
+          <t>30344</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>56096</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>443759</t>
+          <t>456792</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>427374</t>
+          <t>433757</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>452363</t>
+          <t>477431</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>692106</t>
+          <t>728173</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>682753</t>
+          <t>710567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>700042</t>
+          <t>743634</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1135864</t>
+          <t>1184964</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1118885</t>
+          <t>1155477</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1146927</t>
+          <t>1211593</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>730529</t>
+          <t>827556</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>730529</t>
+          <t>827556</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>730529</t>
+          <t>827556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1205574</t>
+          <t>1395519</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1205574</t>
+          <t>1395519</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1205574</t>
+          <t>1395519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>27585</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>43807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>80047</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35009</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>31191</t>
+          <t>30973</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51810</t>
+          <t>47645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>231298</t>
+          <t>217467</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>209823</t>
+          <t>199356</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>238251</t>
+          <t>227391</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>725925</t>
+          <t>773041</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>714933</t>
+          <t>751658</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>733393</t>
+          <t>788024</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>957223</t>
+          <t>990508</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>936213</t>
+          <t>968381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>968105</t>
+          <t>1009041</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>756336</t>
+          <t>842553</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>756336</t>
+          <t>842553</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>756336</t>
+          <t>842553</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>996843</t>
+          <t>1079781</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>996843</t>
+          <t>1079781</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>996843</t>
+          <t>1079781</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>39369</t>
+          <t>291377</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34534</t>
+          <t>258042</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45214</t>
+          <t>334696</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>57619</t>
+          <t>281047</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>252375</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64465</t>
+          <t>313693</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>96988</t>
+          <t>572424</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89010</t>
+          <t>523930</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>104580</t>
+          <t>619603</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>171269</t>
+          <t>172661</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>144891</t>
+          <t>147377</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>199592</t>
+          <t>204223</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>168188</t>
+          <t>173462</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>149128</t>
+          <t>151781</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>193699</t>
+          <t>195337</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>339457</t>
+          <t>346123</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>303797</t>
+          <t>314277</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>374010</t>
+          <t>383790</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2911781</t>
+          <t>2976116</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2883584</t>
+          <t>2930053</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2939945</t>
+          <t>3016944</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3028472</t>
+          <t>3172565</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3001554</t>
+          <t>3138956</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3048473</t>
+          <t>3211252</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5940253</t>
+          <t>6148681</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5905287</t>
+          <t>6088003</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5977000</t>
+          <t>6207709</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3122419</t>
+          <t>3440153</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3122419</t>
+          <t>3440153</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3122419</t>
+          <t>3440153</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3254279</t>
+          <t>3627075</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3254279</t>
+          <t>3627075</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3254279</t>
+          <t>3627075</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6376698</t>
+          <t>7067228</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6376698</t>
+          <t>7067228</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6376698</t>
+          <t>7067228</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
